--- a/docs/perechen-otchetov/obrazcy/ФО-27.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-27.xlsx
@@ -7,18 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-27" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-27'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
+  </numFmts>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +34,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -50,12 +89,32 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009BC2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2FA"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,44 +148,136 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,304 +643,2089 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6.2" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9.4" customWidth="1" min="13" max="13"/>
+    <col width="8.6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-27</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>на 01.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Эпизоды просрочки</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>за период с 01.01.2026 по 30.09.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Кредитов с просрочкой</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Просроченная задолженность</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Дней просрочки</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Наибольшая просрочка, дней</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Средние дни просрочки</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Слой</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Закрыт</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Чем закрыт</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Эпизодов</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>из них</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>закрыты в периоде</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Тянутся на конец</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Просрочено на конец периода</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Длительность, дн.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Средняя длительность</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="41" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>тянулись на начало</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>начались в периоде</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>вылечены</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>иначе</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>вылеченных, дн.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>тянущихся, дн.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>10347.215</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>514</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>149.53846</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Департамент администрирования кредитов</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>4560750</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="4" t="n">
+      <c r="F9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>4326.44</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>514</v>
+      </c>
+      <c r="M9" s="15" t="n"/>
+      <c r="N9" s="16" t="n">
+        <v>83.66667</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Асанов А. К.</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>4326.44</v>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>514</v>
+      </c>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="23" t="n">
+        <v>83.66667</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Тянь-Шань Металл»</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>514</v>
+      </c>
+      <c r="M11" s="29" t="n"/>
+      <c r="N11" s="29" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>№ 20-3/052 от 21.07.2020, KGS</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="27" t="n">
+        <v>514</v>
+      </c>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="29" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 21.04.2025</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>46282</v>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>списанием</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="35" t="n"/>
+      <c r="L13" s="34" t="n">
+        <v>514</v>
+      </c>
+      <c r="M13" s="35" t="n"/>
+      <c r="N13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Кемин-Курулуш»</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <v>2934.5</v>
+      </c>
+      <c r="L14" s="27" t="n">
+        <v>190</v>
+      </c>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="36" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>№ 19-3/061 от 11.04.2019, USD</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>2380</v>
+      </c>
+      <c r="L15" s="27" t="n">
+        <v>190</v>
+      </c>
+      <c r="M15" s="29" t="n"/>
+      <c r="N15" s="36" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 25.03.2026</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="38" t="n">
+        <v>2380</v>
+      </c>
+      <c r="L16" s="34" t="n">
+        <v>190</v>
+      </c>
+      <c r="M16" s="35" t="n"/>
+      <c r="N16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>№ 22-3/014 от 18.03.2022, KGS</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="L17" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="M17" s="29" t="n"/>
+      <c r="N17" s="36" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 03.06.2026</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="38" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="L18" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="M18" s="35" t="n"/>
+      <c r="N18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>№ 24-3/105 от 02.12.2024, KGS</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="L19" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="M19" s="29" t="n"/>
+      <c r="N19" s="36" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 27.08.2026</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="38" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="L20" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="M20" s="35" t="n"/>
+      <c r="N20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>КФХ «Жайыл»</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="28" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L21" s="27" t="n">
+        <v>75</v>
+      </c>
+      <c r="M21" s="29" t="n"/>
+      <c r="N21" s="36" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>№ 23-4/008 от 20.06.2023, KGS</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L22" s="27" t="n">
+        <v>75</v>
+      </c>
+      <c r="M22" s="29" t="n"/>
+      <c r="N22" s="36" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 18.07.2026</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="38" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="L23" s="34" t="n">
+        <v>75</v>
+      </c>
+      <c r="M23" s="35" t="n"/>
+      <c r="N23" s="35" t="n"/>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Сулайман-Тоо Трейд»</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="28" t="n">
+        <v>1061.69</v>
+      </c>
+      <c r="L24" s="27" t="n">
+        <v>62</v>
+      </c>
+      <c r="M24" s="29" t="n"/>
+      <c r="N24" s="36" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>№ 21-1/207 от 15.11.2021, EUR</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="28" t="n">
+        <v>1061.69</v>
+      </c>
+      <c r="L25" s="27" t="n">
+        <v>62</v>
+      </c>
+      <c r="M25" s="29" t="n"/>
+      <c r="N25" s="36" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 31.07.2026</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="38" t="n">
+        <v>1061.69</v>
+      </c>
+      <c r="L26" s="34" t="n">
+        <v>62</v>
+      </c>
+      <c r="M26" s="35" t="n"/>
+      <c r="N26" s="35" t="n"/>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Тянь-Шань Строй»</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="28" t="n">
+        <v>180.85</v>
+      </c>
+      <c r="L27" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="M27" s="29" t="n"/>
+      <c r="N27" s="36" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>№ 22-1/045 от 03.02.2022, KGS</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="28" t="n">
+        <v>180.85</v>
+      </c>
+      <c r="L28" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="M28" s="29" t="n"/>
+      <c r="N28" s="36" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 11.09.2026</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="32" t="n"/>
+      <c r="E29" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="38" t="n">
+        <v>180.85</v>
+      </c>
+      <c r="L29" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="M29" s="35" t="n"/>
+      <c r="N29" s="35" t="n"/>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Департамент регионального развития</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>6020.775</v>
+      </c>
+      <c r="L30" s="13" t="n">
         <v>409</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>180.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Отраслевой департамент промышленности</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+      <c r="M30" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="N30" s="16" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Жумабаев Р. С.</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="4" t="n">
+      <c r="H31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="21" t="n">
+        <v>1967.4</v>
+      </c>
+      <c r="L31" s="20" t="n">
         <v>409</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>238.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Нарын-Агро» · № 21-2/077 от 18.05.2021</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>1024300</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="M31" s="23" t="n">
+        <v>94</v>
+      </c>
+      <c r="N31" s="23" t="n">
+        <v>198.75</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Нарын-Агро»</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="28" t="n">
+        <v>1024.3</v>
+      </c>
+      <c r="L32" s="27" t="n">
         <v>409</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="M32" s="29" t="n"/>
+      <c r="N32" s="36" t="n">
         <v>409</v>
       </c>
-      <c r="F7" s="9" t="n">
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>№ 21-2/077 от 18.05.2021, KGS</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="25" t="n"/>
+      <c r="E33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="28" t="n">
+        <v>1024.3</v>
+      </c>
+      <c r="L33" s="27" t="n">
         <v>409</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Талас-Бал» · № 23-4/021 от 21.08.2023</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>873000</v>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="M33" s="29" t="n"/>
+      <c r="N33" s="36" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 18.08.2025</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="38" t="n">
+        <v>1024.3</v>
+      </c>
+      <c r="L34" s="34" t="n">
+        <v>409</v>
+      </c>
+      <c r="M34" s="35" t="n"/>
+      <c r="N34" s="35" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Талас-Бал»</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="28" t="n">
+        <v>873</v>
+      </c>
+      <c r="L35" s="27" t="n">
         <v>260</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="M35" s="29" t="n"/>
+      <c r="N35" s="36" t="n">
         <v>260</v>
       </c>
-      <c r="F8" s="9" t="n">
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>№ 23-4/021 от 21.08.2023, KGS</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="28" t="n">
+        <v>873</v>
+      </c>
+      <c r="L36" s="27" t="n">
         <v>260</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Нарын-Сүт» · № 23-5/071 от 09.08.2023</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>551000</v>
-      </c>
-      <c r="D9" s="8" t="n">
+      <c r="M36" s="29" t="n"/>
+      <c r="N36" s="36" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 14.01.2026</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="38" t="n">
+        <v>873</v>
+      </c>
+      <c r="L37" s="34" t="n">
+        <v>260</v>
+      </c>
+      <c r="M37" s="35" t="n"/>
+      <c r="N37" s="35" t="n"/>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Иманалиев Бакыт Тологонович</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="25" t="n"/>
+      <c r="E38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="28" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L38" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="M38" s="29" t="n"/>
+      <c r="N38" s="36" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>№ 24-2/077 от 14.05.2024, KGS</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="25" t="n"/>
+      <c r="E39" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="28" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L39" s="27" t="n">
+        <v>95</v>
+      </c>
+      <c r="M39" s="29" t="n"/>
+      <c r="N39" s="36" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 28.06.2026</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="32" t="n"/>
+      <c r="E40" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="38" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L40" s="34" t="n">
+        <v>95</v>
+      </c>
+      <c r="M40" s="35" t="n"/>
+      <c r="N40" s="35" t="n"/>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>КФХ «Ак-Суу»</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="25" t="n"/>
+      <c r="E41" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="28" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L41" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="M41" s="36" t="n">
+        <v>94</v>
+      </c>
+      <c r="N41" s="36" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>№ 20-6/027 от 12.05.2020, KGS</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="28" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L42" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="M42" s="36" t="n">
+        <v>94</v>
+      </c>
+      <c r="N42" s="36" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 12.05.2026</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
+        <is>
+          <t>погашением</t>
+        </is>
+      </c>
+      <c r="E43" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="35" t="n"/>
+      <c r="L43" s="34" t="n">
+        <v>94</v>
+      </c>
+      <c r="M43" s="35" t="n"/>
+      <c r="N43" s="35" t="n"/>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 31.08.2026</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="n"/>
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="38" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="L44" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="M44" s="35" t="n"/>
+      <c r="N44" s="35" t="n"/>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Осмонов Б. Т.</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="21" t="n">
+        <v>3502.375</v>
+      </c>
+      <c r="L45" s="20" t="n">
+        <v>245</v>
+      </c>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="23" t="n">
+        <v>228.5</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Кербен-Жибек»</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="28" t="n">
+        <v>1771.875</v>
+      </c>
+      <c r="L46" s="27" t="n">
+        <v>245</v>
+      </c>
+      <c r="M46" s="29" t="n"/>
+      <c r="N46" s="36" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>№ 20-5/118 от 23.06.2020, USD</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n"/>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="25" t="n"/>
+      <c r="E47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="28" t="n">
+        <v>1771.875</v>
+      </c>
+      <c r="L47" s="27" t="n">
+        <v>245</v>
+      </c>
+      <c r="M47" s="29" t="n"/>
+      <c r="N47" s="36" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 29.01.2026</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="n"/>
+      <c r="D48" s="32" t="n"/>
+      <c r="E48" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="38" t="n">
+        <v>1771.875</v>
+      </c>
+      <c r="L48" s="34" t="n">
+        <v>245</v>
+      </c>
+      <c r="M48" s="35" t="n"/>
+      <c r="N48" s="35" t="n"/>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Ош-Текстиль»</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="28" t="n">
+        <v>1730.5</v>
+      </c>
+      <c r="L49" s="27" t="n">
+        <v>212</v>
+      </c>
+      <c r="M49" s="29" t="n"/>
+      <c r="N49" s="36" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>№ 21-5/203 от 09.09.2021, KGS</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="n"/>
+      <c r="C50" s="26" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="28" t="n">
+        <v>1730.5</v>
+      </c>
+      <c r="L50" s="27" t="n">
+        <v>212</v>
+      </c>
+      <c r="M50" s="29" t="n"/>
+      <c r="N50" s="36" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 03.03.2026</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="n"/>
+      <c r="D51" s="32" t="n"/>
+      <c r="E51" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="38" t="n">
+        <v>1730.5</v>
+      </c>
+      <c r="L51" s="34" t="n">
+        <v>212</v>
+      </c>
+      <c r="M51" s="35" t="n"/>
+      <c r="N51" s="35" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Токтогулова Г. А.</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="21" t="n">
+        <v>551</v>
+      </c>
+      <c r="L52" s="20" t="n">
         <v>190</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="M52" s="22" t="n"/>
+      <c r="N52" s="23" t="n">
         <v>190</v>
       </c>
-      <c r="F9" s="9" t="n">
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>ОсОО «Нарын-Сүт»</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="n"/>
+      <c r="C53" s="26" t="n"/>
+      <c r="D53" s="25" t="n"/>
+      <c r="E53" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="28" t="n">
+        <v>551</v>
+      </c>
+      <c r="L53" s="27" t="n">
         <v>190</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Иманалиев Бакыт Тологонович · № 24-2/077 от 14.05.2024</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>51700</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Региональное представительство «Ош»</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1730500</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="4" t="n">
-        <v>212</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Ош-Текстиль» · № 21-5/203 от 09.09.2021</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1730500</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>212</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>212</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Департамент администрирования кредитов</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>330250</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>КФХ «Жайыл» · № 23-4/008 от 20.06.2023</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>149400</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>ОсОО «Тянь-Шань Строй» · № 22-1/045 от 03.02.2022</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>180850</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="M53" s="29" t="n"/>
+      <c r="N53" s="36" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>№ 23-5/071 от 09.08.2023, KGS</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="26" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="28" t="n">
+        <v>551</v>
+      </c>
+      <c r="L54" s="27" t="n">
+        <v>190</v>
+      </c>
+      <c r="M54" s="29" t="n"/>
+      <c r="N54" s="36" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>Эпизод с 25.03.2026</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>свободный</t>
+        </is>
+      </c>
+      <c r="C55" s="37" t="n"/>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="38" t="n">
+        <v>551</v>
+      </c>
+      <c r="L55" s="34" t="n">
+        <v>190</v>
+      </c>
+      <c r="M55" s="35" t="n"/>
+      <c r="N55" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="13">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-27 · сформировал Асанов А. К. 06.10.2026 11:40 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -799,7 +2735,177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>ФО-27 «Эпизоды просрочки за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>01.01.2026 – 30.09.2026 (по умолчанию — с начала года по вчерашний день)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>Что попадает</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>эпизоды просрочки, открытые хотя бы один день периода; просроченная часть и длительность тянущихся — на 01.10.2026 (данные на конец 30.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Слой</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>все — свободный и по решению суда</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>Департамент → Куратор → Заёмщик → Кредит → эпизод</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>USD — 87,50000, EUR — 101,50000 на 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>Период закрыт</t>
+        </is>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>январь–сентябрь 2026 закрыты, сентябрь — 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>06.10.2026 11:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Асанов А. К.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками. Итоги считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -808,358 +2914,619 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ФО-27 «Средняя просрочка по департаментам» — карточка</t>
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>ФО-27 «Эпизоды просрочки за период» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="44" t="inlineStr">
         <is>
           <t>ФО-27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Средняя просрочка по департаментам</t>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>Эпизоды просрочки за период</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Портфель</t>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>Кредит</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶646, ¶659; Порядок №41 п. 6 пп. 1, 6, 7, п. 16; ТЗ 18 §9.5; ТЗ 19 §3.1; ТЗ 24</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="11" ht="165" customHeight="1">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Руководству департаментов — как долго в среднем заёмщики подразделения находятся в просрочке; показатель для контроля работы с просроченной задолженностью.</t>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Руководству Департамента администрирования кредитов и Департамента регионального развития, кураторам и отделу по работе с проблемными кредитами — как долго кредиты находятся в просрочке и как она лечится: сколько кредитов вышло в просрочку за период, сколько эпизодов вылечено погашением и за сколько дней, сколько закрыто иначе (списанием, реструктуризацией, переводом в слой по решению суда), сколько тянется на конец периода и как долго (Порядок №41 п. 6 пп. 1, 6, 7). Эпизод — отрезок непрерывной просрочки одного слоя долга; его длительность считается от начала непрерывной просрочки и после частичного погашения больше дней просрочки ФО-01, которые идут от самого раннего неоплаченного срока. Суммы и дни просрочки на дату — ФО-01; счётчики «вышли в просрочку · вылечены» — плитки дашборда, список эпизодов за ними — здесь. Новая форма: в старой системе такого отчёта не было; прежнее название в перечне — «Средняя просрочка по департаментам» (средние дни просрочки по подразделениям на дату).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>На дату; по требованию. По умолчанию — сегодня, по данным на конец предыдущего дня. Официальным документом становится по требованию получателя.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>За период, по требованию; по умолчанию — с начала года по вчерашний день. Можно выбрать любой период: за прошлый месяц — кто вышел в просрочку и кто вылечен в месяце.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="180" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>• Дата — сегодня (данные на конец предыдущего дня; 01.10.2026 = данные на конец 30.09.2026)
-• Подразделение — все</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>• Период — с начала года по вчерашний день; можно выбрать любой. В отчёт попадает эпизод, открытый хотя бы один день периода: начался не позже конца периода и не закрыт до его начала
+• Слой — все (свободный и по решению суда)
+• Единица — тыс. сом (можно выбрать «сом»)
+• Разрезы — до шести уровней в любом порядке; по умолчанию департамент → куратор → заёмщик → кредит → эпизод. Доступны: департамент, отдел, куратор, область, район, категория риска, группа платёжеспособности, тип проекта, валюта, слой, чем закрыт, месяц начала, заёмщик, кредит
+• Отбор — по любому из разрезов; только начавшиеся в периоде; только закрытые в периоде; только тянущиеся на конец периода; длительность от N дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="255" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Подразделение → кредит с просрочкой. Подытоги по подразделению, сверху ИТОГО. Подразделения — по убыванию средних дней просрочки, кредиты — по убыванию дней просрочки. Кредиты без просрочки в отчёт не входят. Показатель «Средние дни просрочки» принят в системе, нормой не определён. Округление математическое (половина вверх).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>Строка детали — эпизод просрочки: отрезок, на котором у одного слоя долга кредита непрерывно есть просроченная часть; ключ — кредит, слой, начало. Над эпизодами всегда строка кредита, над ней — строка заёмщика, даже при одном кредите и одном эпизоде. В отчёт попадает эпизод, открытый хотя бы один день периода; эпизоды обоих слоёв — свободного и по каждому решению суда; закрытый кредит — со своими эпизодами, эпизод закрывается не позже даты закрытия кредита. Возврат в просрочку после закрытия — новый эпизод. Эпизоды отчёт читает у объекта статистики «Эпизод просрочки» (их отдаёт расчётное ядро), а не строит сам; поправка задним числом, сдвинувшая начало, даёт другой эпизод, прежний из отчёта исчезает. Эпизод кредита из старой системы, начавшийся до переноса, — с пометкой «начало по данным переноса» в колонке «Слой». Счётчики — признаки эпизода: 1 в своей колонке, в строке выше — сумма; тянулись на начало + начались в периоде = эпизодов = вылечены + закрыты иначе + тянутся на конец. Над кредитами разрезы, по умолчанию департамент → куратор → заёмщик; подразделение и куратор — кредита на конец периода, у закрытого — на дату закрытия. Первая строка — ИТОГО. Порядок: департаменты — по оргструктуре; кураторы — по алфавиту фамилии; заёмщики и кредиты — по наибольшей длительности эпизодов от большего, при равных — заёмщики по алфавиту наименования без организационной формы, кредиты по дате договора; эпизоды кредита — по началу. Суммы — в тыс. сом; валютный кредит — в сомах по курсу последнего дня периода, строки в валюте нет, валюта — в наименовании кредита. Печать — A4 альбомная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>по умолчанию: Департамент → Куратор → Заёмщик → Кредит → эпизод просрочки; можно выбрать: Департамент, Отдел, Куратор, Область, Район, Категория риска, Группа платёжеспособности, Тип проекта, Валюта, Слой, Чем закрыт, Месяц начала, Заёмщик, Кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>Эпизодов просрочки за период по условиям отбора нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Средняя просрочка по департаментам» (средние дни просрочки по подразделениям на дату); в старой системе такого отчёта не было. Строка — эпизод просрочки (кредит × слой долга × начало) под департаментом, куратором, заёмщиком и кредитом: слой, закрытие и чем закрыт, длительность; счётчики «тянулись на начало · начались · вылечены · закрыты иначе · тянутся на конец», просрочено на конец периода, средняя длительность вылеченных и тянущихся; суммы и дни просрочки на дату — ФО-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr"/>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>подразделение или заёмщик с номером договора — по уровню строки</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Кредитов с просрочкой</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>число кредитов, у которых дней просрочки больше нуля</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Просроченная задолженность</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>просроченные основная сумма, проценты и штрафы, сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Дней просрочки</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr"/>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>число дней от наиболее ранней неоплаченной даты платежа до даты состояния; первый день просрочки — день 1 (Порядок №41 п. 16 пп. 1); в итоговых строках пусто</t>
+      <c r="B22" s="44" t="inlineStr"/>
+      <c r="C22" s="44" t="inlineStr">
+        <is>
+          <t>департамент, куратор, заёмщик, кредит «№ … от …, валюта» или эпизод «Эпизод с ДД.ММ.ГГГГ» — по уровню строки; дата в имени эпизода — его начало: срок самого раннего неисполненного обязательства, с которого просрочка слоя непрерывна (день, на конец которого просроченная часть появилась; первый день просрочки по Порядку №41 п. 16 — следующий)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Наибольшая просрочка, дней</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr"/>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>наибольшее число дней просрочки среди кредитов строки</t>
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>Слой</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr"/>
+      <c r="C23" s="44" t="inlineStr">
+        <is>
+          <t>слой долга эпизода: «свободный» или «по решению суда № … от …»; у одного кредита эпизоды разных слоёв — разные строки; у строк выше эпизода пусто</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Средние дни просрочки</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr"/>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>принято: сумма дней просрочки всех кредитов с просрочкой / число этих кредитов, один знак, округление математическое (половина вверх); норма показатель не определяет; для подразделения и ИТОГО считается по кредитам, а не как среднее средних</t>
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>Закрыт</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr"/>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>первый день, на конец которого просроченной части слоя нет; у эпизода, тянущегося на конец периода, пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>Чем закрыт</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr"/>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>погашением (вылечен) · списанием · реструктуризацией · переводом в другой слой · закрытием кредита — по движениям дня закрытия, при нескольких — по старшинству списание → реструктуризация → перевод → погашение; у тянущегося пусто</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>Эпизодов</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr"/>
+      <c r="C26" s="44" t="inlineStr">
+        <is>
+          <t>1 в строке эпизода; в строке выше — число эпизодов; = тянулись на начало + начались в периоде = вылечены + закрыты иначе + тянутся на конец</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>тянулись на начало</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>из них</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="inlineStr">
+        <is>
+          <t>1, если эпизод начался до первого дня периода</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>начались в периоде</t>
+        </is>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>из них</t>
+        </is>
+      </c>
+      <c r="C28" s="44" t="inlineStr">
+        <is>
+          <t>1, если начало эпизода — в периоде: кредит вышел в просрочку</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>вылечены</t>
+        </is>
+      </c>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>закрыты в периоде</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>1, если эпизод закрыт в периоде погашением</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>иначе</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>закрыты в периоде</t>
+        </is>
+      </c>
+      <c r="C30" s="44" t="inlineStr">
+        <is>
+          <t>1, если эпизод закрыт в периоде списанием, реструктуризацией, переводом в другой слой или закрытием кредита</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>Тянутся на конец</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="inlineStr"/>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>1, если на конец периода эпизод не закрыт</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>Просрочено на конец периода</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="inlineStr"/>
+      <c r="C32" s="44" t="inlineStr">
+        <is>
+          <t>просроченная часть слоя на конец периода — основная сумма, проценты и штрафы — у тянущегося эпизода; у закрытого пусто; в строке выше — сумма; валютный кредит — в сомах по курсу последнего дня периода; у кредита с одним слоем = «Просроченная задолженность» ФО-01 на дату, следующую за концом периода</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>Длительность, дн.</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="inlineStr"/>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>у эпизода: закрытого — закрытие минус начало, без дня закрытия; тянущегося — дата состояния (день после конца периода) минус начало, как дни просрочки ФО-01; в строке выше — наибольшая длительность эпизодов строки</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>вылеченных, дн.</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>Средняя длительность</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>сумма длительностей эпизодов строки, закрытых в периоде погашением, делённая на их число, один знак; считается по эпизодам, а не как среднее средних; у эпизода и при отсутствии вылеченных — пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>тянущихся, дн.</t>
+        </is>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>Средняя длительность</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="inlineStr">
+        <is>
+          <t>то же по эпизодам, тянущимся на конец периода, по их длительности на дату состояния; у эпизода и при отсутствии тянущихся — пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="45" t="inlineStr">
         <is>
           <t>Правила проверки</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="38" ht="75" customHeight="1">
+      <c r="A38" s="43" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>„Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>Январь–сентябрь 2026 (01.01.2026 – 30.09.2026): 15 эпизодов у 14 кредитов 12 заёмщиков; тянулись на начало 2 (КЗ-05 с 18.08.2025, КЗ-08 с 21.04.2025), начались в периоде 13; вылечен 1 — КЗ-24 № 20-6/027, 12.05.2026 – 14.08.2026, 94 дня; закрыт иначе 1 — КЗ-08 № 20-3/052 списанием 17.09.2026, 514 дней (= ФО-11); тянутся на конец 13 — те же 13 кредитов, что в ФО-01 на 01.10.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>„Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>Тождество в каждой строке: «тянулись на начало» + «начались в периоде» = «Эпизодов» = «вылечены» + «иначе» + «Тянутся на конец»; строка выше = сумма строк на уровень ниже по счётчикам и сумме. ДАК: 7 = 1 + 6 = 0 + 1 + 6; ДРР: 8 = 1 + 7 = 1 + 0 + 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="43" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>«Просрочено на конец периода» в ИТОГО = ИТОГО ФО-01 на 01.10.2026: 10 347,215 тыс. сом; ДАК 4 326,440, ДРР 6 020,775; у кредита = «Просроченная задолженность» ФО-01; валютные — по курсу 30.09.2026: КЗ-21 № 19-3/061 27,200 тыс. USD = 2 380,000, КЗ-23 20,250 тыс. USD = 1 771,875, КЗ-22 10,460 тыс. EUR = 1 061,690. У закрытых эпизодов (КЗ-08, первый эпизод КЗ-24) пусто.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
+      <c r="A41" s="43" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>„Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>Начало эпизода — срок самого раннего неисполненного обязательства, с которого просрочка непрерывна: КЗ-02 — 11.09.2026 (первый день просрочки по Порядку №41 п. 16 — 12.09.2026), КЗ-24 — 31.08.2026 (штрафы по претензии), КЗ-21 — 25.03.2026, 03.06.2026, 27.08.2026. Длительность тянущегося — 01.10.2026 минус начало: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-23 — 245, КЗ-10 — 260, КЗ-05 — 409; КЗ-21 — 190, 120, 35; КЗ-22 — 62; КЗ-24 — 31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1">
+      <c r="A42" s="43" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>Длительность не меньше дней просрочки ФО-01 на ту же дату и равна им, пока самый ранний неоплаченный срок не гасился частично; частичного погашения в наборе нет, поэтому у 13 тянущихся эпизодов длительность = дням ФО-01. Если бы КЗ-03 внёс сумму июльского взноса, а августовский остался неоплаченным, эпизод продолжился бы с 18.07.2026, а дни просрочки ФО-01 считались бы от августовского срока.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>Средняя длительность тянущихся — по эпизодам, а не как среднее средних: ИТОГО 1 944 / 13 = 149,5; ДАК 502 / 6 = 83,7; ДРР 1 442 / 7 = 206,0; Жумабаев Р. С. (КЗ-05, 10, 09, 24) 795 / 4 = 198,8; Осмонов Б. Т. 457 / 2 = 228,5. Вылеченных: ИТОГО, ДРР, Жумабаев Р. С., КЗ-24 — 94,0; в ДАК вылеченных нет — пусто. «Длительность» в строке выше — наибольшая: ИТОГО и ДАК 514 (КЗ-08), ДРР 409 (КЗ-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>КЗ-24 — два эпизода одного свободного слоя: 12.05.2026 – 14.08.2026 по основной сумме и процентам, закрыт погашением (вылечен); с 31.08.2026 по штрафам 18,400 — тянется. Строка кредита — 2 эпизода, наибольшая длительность 94.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>КЗ-08: эпизод закрыт 17.09.2026 «списанием» (списание и закрытие кредита в один день — причина по старшинству); кредит закрыт, в ФО-01 и ФО-02 на 01.10.2026 его нет, здесь он есть под Асановым А. К. — куратором на дату закрытия.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>Не попадают: КЗ-15 (погашен 18.09.2026 без просрочки), КЗ-07 (перевод долга без просрочки), КЗ-06 (реструктуризация без просроченных сумм), КЗ-01, 11, 12, 13, 14, 17, 20, 25 — просрочки в периоде не было; КЗ-16, 18, 26 — нет просрочки и нет долга в периоде.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026 (период выбран): 14 эпизодов — тянулись на 01.09.2026 13, начался 1 (КЗ-02 с 11.09.2026); вылечено 0, закрыт иначе 1 (КЗ-08), тянутся на конец 13; первый эпизод КЗ-24 закрыт 14.08.2026 — до начала периода — и в отчёт за сентябрь не входит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>Отбор «только тянущиеся на конец периода» — 13 эпизодов, «Просрочено на конец периода» 10 347,215 = ФО-01; под заголовком строка «Отбор: только тянущиеся на конец периода».</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>Периоды закрыты: эпизоды и длительности на 30.09.2026 после закрытия не меняются; поправка задним числом в открытом периоде, сдвинувшая начало, заменяет эпизод другим.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="28">
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
